--- a/data/output/tabela_de_sais_concatenada.xlsx
+++ b/data/output/tabela_de_sais_concatenada.xlsx
@@ -7888,13 +7888,13 @@
         <v>0.101325</v>
       </c>
       <c r="G178" t="n">
-        <v>41.13470239677886</v>
+        <v>4.471342150529864</v>
       </c>
       <c r="H178" t="n">
-        <v>19.90633784301958</v>
+        <v>2.163818923536229</v>
       </c>
       <c r="I178" t="n">
-        <v>61.04104023979845</v>
+        <v>6.635161074066094</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23838,7 +23838,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E558" t="n">
@@ -23851,10 +23851,10 @@
         <v>3.454625224982467</v>
       </c>
       <c r="H558" t="n">
-        <v>0.4218221819596006</v>
+        <v>0.8687576045563753</v>
       </c>
       <c r="I558" t="n">
-        <v>3.876447406942067</v>
+        <v>4.323382829538843</v>
       </c>
       <c r="J558" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E559" t="n">
@@ -23893,10 +23893,10 @@
         <v>2.238597220852675</v>
       </c>
       <c r="H559" t="n">
-        <v>1.128587537561469</v>
+        <v>2.324365686766997</v>
       </c>
       <c r="I559" t="n">
-        <v>3.367184758414145</v>
+        <v>4.562962907619672</v>
       </c>
       <c r="J559" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23922,7 +23922,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E560" t="n">
@@ -23935,10 +23935,10 @@
         <v>1.086762553585705</v>
       </c>
       <c r="H560" t="n">
-        <v>2.143468936398554</v>
+        <v>4.414549585742161</v>
       </c>
       <c r="I560" t="n">
-        <v>3.230231489984259</v>
+        <v>5.501312139327866</v>
       </c>
       <c r="J560" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E561" t="n">
@@ -23977,10 +23977,10 @@
         <v>5.741130462345882</v>
       </c>
       <c r="H561" t="n">
-        <v>0.1258600825529257</v>
+        <v>0.2592132621380717</v>
       </c>
       <c r="I561" t="n">
-        <v>5.866990544898807</v>
+        <v>6.000343724483954</v>
       </c>
       <c r="J561" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E562" t="n">
@@ -24019,10 +24019,10 @@
         <v>4.786348430034455</v>
       </c>
       <c r="H562" t="n">
-        <v>0.1704784106202113</v>
+        <v>0.3511062764669341</v>
       </c>
       <c r="I562" t="n">
-        <v>4.956826840654667</v>
+        <v>5.13745470650139</v>
       </c>
       <c r="J562" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E563" t="n">
@@ -24061,10 +24061,10 @@
         <v>3.556164427147952</v>
       </c>
       <c r="H563" t="n">
-        <v>0.4645841936999103</v>
+        <v>0.9568274701877684</v>
       </c>
       <c r="I563" t="n">
-        <v>4.020748620847862</v>
+        <v>4.51299189733572</v>
       </c>
       <c r="J563" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E564" t="n">
@@ -24103,10 +24103,10 @@
         <v>1.375019269801301</v>
       </c>
       <c r="H564" t="n">
-        <v>1.840493258485559</v>
+        <v>3.790560531966543</v>
       </c>
       <c r="I564" t="n">
-        <v>3.21551252828686</v>
+        <v>5.165579801767844</v>
       </c>
       <c r="J564" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E565" t="n">
@@ -24145,10 +24145,10 @@
         <v>1.133049625345683</v>
       </c>
       <c r="H565" t="n">
-        <v>1.984983665704805</v>
+        <v>4.088143602335256</v>
       </c>
       <c r="I565" t="n">
-        <v>3.118033291050489</v>
+        <v>5.221193227680939</v>
       </c>
       <c r="J565" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E566" t="n">
@@ -24187,10 +24187,10 @@
         <v>5.85812932902108</v>
       </c>
       <c r="H566" t="n">
-        <v>0.02723529854471813</v>
+        <v>0.05609205427075701</v>
       </c>
       <c r="I566" t="n">
-        <v>5.885364627565798</v>
+        <v>5.914221383291837</v>
       </c>
       <c r="J566" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E567" t="n">
@@ -24229,10 +24229,10 @@
         <v>5.870091093547692</v>
       </c>
       <c r="H567" t="n">
-        <v>0.06246663891065676</v>
+        <v>0.1286522376149192</v>
       </c>
       <c r="I567" t="n">
-        <v>5.932557732458348</v>
+        <v>5.998743331162611</v>
       </c>
       <c r="J567" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E568" t="n">
@@ -24271,10 +24271,10 @@
         <v>4.944512470156528</v>
       </c>
       <c r="H568" t="n">
-        <v>0.1384059278912901</v>
+        <v>0.2850518714133329</v>
       </c>
       <c r="I568" t="n">
-        <v>5.082918398047817</v>
+        <v>5.22956434156986</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E569" t="n">
@@ -24313,10 +24313,10 @@
         <v>3.584737860439128</v>
       </c>
       <c r="H569" t="n">
-        <v>0.4776351773357436</v>
+        <v>0.9837064295348062</v>
       </c>
       <c r="I569" t="n">
-        <v>4.062373037774871</v>
+        <v>4.568444289973934</v>
       </c>
       <c r="J569" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E570" t="n">
@@ -24355,10 +24355,10 @@
         <v>2.688341457582769</v>
       </c>
       <c r="H570" t="n">
-        <v>0.8827529111281205</v>
+        <v>1.818060636176505</v>
       </c>
       <c r="I570" t="n">
-        <v>3.57109436871089</v>
+        <v>4.506402093759274</v>
       </c>
       <c r="J570" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -24384,7 +24384,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E571" t="n">
@@ -24397,10 +24397,10 @@
         <v>1.294656353442645</v>
       </c>
       <c r="H571" t="n">
-        <v>1.860164443573358</v>
+        <v>3.831074028806068</v>
       </c>
       <c r="I571" t="n">
-        <v>3.154820797016003</v>
+        <v>5.125730382248713</v>
       </c>
       <c r="J571" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -24426,7 +24426,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E572" t="n">
@@ -24439,10 +24439,10 @@
         <v>0.885777074533239</v>
       </c>
       <c r="H572" t="n">
-        <v>2.219900054305582</v>
+        <v>4.571962158494996</v>
       </c>
       <c r="I572" t="n">
-        <v>3.105677128838821</v>
+        <v>5.457739233028235</v>
       </c>
       <c r="J572" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E573" t="n">
@@ -24481,10 +24481,10 @@
         <v>0.07192842144990055</v>
       </c>
       <c r="H573" t="n">
-        <v>3.014389648142153</v>
+        <v>6.208241391559444</v>
       </c>
       <c r="I573" t="n">
-        <v>3.086318069592053</v>
+        <v>6.280169813009344</v>
       </c>
       <c r="J573" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -24510,7 +24510,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E574" t="n">
@@ -24523,10 +24523,10 @@
         <v>6.332857798349046</v>
       </c>
       <c r="H574" t="n">
-        <v>0.03739362856506764</v>
+        <v>0.07701349186271648</v>
       </c>
       <c r="I574" t="n">
-        <v>6.370251426914114</v>
+        <v>6.409871290211763</v>
       </c>
       <c r="J574" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E575" t="n">
@@ -24565,10 +24565,10 @@
         <v>5.612768199147018</v>
       </c>
       <c r="H575" t="n">
-        <v>0.1248655265860526</v>
+        <v>0.2571649391803646</v>
       </c>
       <c r="I575" t="n">
-        <v>5.737633725733071</v>
+        <v>5.869933138327383</v>
       </c>
       <c r="J575" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E576" t="n">
@@ -24607,10 +24607,10 @@
         <v>4.788927216632509</v>
       </c>
       <c r="H576" t="n">
-        <v>0.202935661124258</v>
+        <v>0.4179531242723024</v>
       </c>
       <c r="I576" t="n">
-        <v>4.991862877756767</v>
+        <v>5.206880340904812</v>
       </c>
       <c r="J576" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24636,7 +24636,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E577" t="n">
@@ -24649,10 +24649,10 @@
         <v>3.725043917710148</v>
       </c>
       <c r="H577" t="n">
-        <v>0.5081527970056202</v>
+        <v>1.046558539487866</v>
       </c>
       <c r="I577" t="n">
-        <v>4.233196714715769</v>
+        <v>4.771602457198014</v>
       </c>
       <c r="J577" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E578" t="n">
@@ -24691,10 +24691,10 @@
         <v>3.470104891900569</v>
       </c>
       <c r="H578" t="n">
-        <v>0.5829607213632763</v>
+        <v>1.200628088094525</v>
       </c>
       <c r="I578" t="n">
-        <v>4.053065613263845</v>
+        <v>4.670732979995094</v>
       </c>
       <c r="J578" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -24720,7 +24720,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E579" t="n">
@@ -24733,10 +24733,10 @@
         <v>2.325374212641658</v>
       </c>
       <c r="H579" t="n">
-        <v>1.22097148813301</v>
+        <v>2.514633678898508</v>
       </c>
       <c r="I579" t="n">
-        <v>3.546345700774667</v>
+        <v>4.840007891540166</v>
       </c>
       <c r="J579" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -24762,7 +24762,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E580" t="n">
@@ -24775,10 +24775,10 @@
         <v>1.186721703011436</v>
       </c>
       <c r="H580" t="n">
-        <v>2.076732655903669</v>
+        <v>4.277103871269774</v>
       </c>
       <c r="I580" t="n">
-        <v>3.263454358915105</v>
+        <v>5.463825574281209</v>
       </c>
       <c r="J580" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E581" t="n">
@@ -24817,10 +24817,10 @@
         <v>1.055598285801769</v>
       </c>
       <c r="H581" t="n">
-        <v>2.186630511656415</v>
+        <v>4.503442366476698</v>
       </c>
       <c r="I581" t="n">
-        <v>3.242228797458184</v>
+        <v>5.559040652278467</v>
       </c>
       <c r="J581" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -24846,7 +24846,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E582" t="n">
@@ -24859,10 +24859,10 @@
         <v>6.702564774415161</v>
       </c>
       <c r="H582" t="n">
-        <v>0.05465830904682467</v>
+        <v>0.1125707079130543</v>
       </c>
       <c r="I582" t="n">
-        <v>6.757223083461986</v>
+        <v>6.815135482328215</v>
       </c>
       <c r="J582" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E583" t="n">
@@ -24901,10 +24901,10 @@
         <v>5.692857772456023</v>
       </c>
       <c r="H583" t="n">
-        <v>0.09550981204888673</v>
+        <v>0.1967058136719023</v>
       </c>
       <c r="I583" t="n">
-        <v>5.788367584504909</v>
+        <v>5.889563586127925</v>
       </c>
       <c r="J583" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -24930,7 +24930,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E584" t="n">
@@ -24943,10 +24943,10 @@
         <v>4.847774645072284</v>
       </c>
       <c r="H584" t="n">
-        <v>0.2833141427350817</v>
+        <v>0.5834954312645544</v>
       </c>
       <c r="I584" t="n">
-        <v>5.131088787807365</v>
+        <v>5.431270076336839</v>
       </c>
       <c r="J584" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -24972,7 +24972,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E585" t="n">
@@ -24985,10 +24985,10 @@
         <v>3.385198484157746</v>
       </c>
       <c r="H585" t="n">
-        <v>0.9100326712435243</v>
+        <v>1.874244260614255</v>
       </c>
       <c r="I585" t="n">
-        <v>4.29523115540127</v>
+        <v>5.259442744772001</v>
       </c>
       <c r="J585" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E586" t="n">
@@ -25027,10 +25027,10 @@
         <v>2.250535718649931</v>
       </c>
       <c r="H586" t="n">
-        <v>1.494130940736286</v>
+        <v>3.077215169049448</v>
       </c>
       <c r="I586" t="n">
-        <v>3.744666659386217</v>
+        <v>5.327750887699379</v>
       </c>
       <c r="J586" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E587" t="n">
@@ -25069,10 +25069,10 @@
         <v>1.152443901680162</v>
       </c>
       <c r="H587" t="n">
-        <v>2.422796952244844</v>
+        <v>4.989835448625847</v>
       </c>
       <c r="I587" t="n">
-        <v>3.575240853925007</v>
+        <v>6.142279350306009</v>
       </c>
       <c r="J587" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E588" t="n">
@@ -25111,10 +25111,10 @@
         <v>7.913184962055364</v>
       </c>
       <c r="H588" t="n">
-        <v>0.01312259859179645</v>
+        <v>0.0270264528650506</v>
       </c>
       <c r="I588" t="n">
-        <v>7.926307560647161</v>
+        <v>7.940211414920415</v>
       </c>
       <c r="J588" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E589" t="n">
@@ -25153,10 +25153,10 @@
         <v>4.906563136254144</v>
       </c>
       <c r="H589" t="n">
-        <v>0.3266653263792751</v>
+        <v>0.6727787171326742</v>
       </c>
       <c r="I589" t="n">
-        <v>5.233228462633419</v>
+        <v>5.579341853386818</v>
       </c>
       <c r="J589" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>MgSO4</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Mg_1_SO4_1</t>
+          <t>Na_1_Cl_1</t>
         </is>
       </c>
       <c r="E590" t="n">
@@ -25195,10 +25195,10 @@
         <v>3.806369255665571</v>
       </c>
       <c r="H590" t="n">
-        <v>0.8808254725454813</v>
+        <v>1.814091008694601</v>
       </c>
       <c r="I590" t="n">
-        <v>4.687194728211053</v>
+        <v>5.620460264360172</v>
       </c>
       <c r="J590" t="inlineStr">
         <is>
@@ -37666,13 +37666,13 @@
         <v>0.101325</v>
       </c>
       <c r="G887" t="n">
-        <v>35.96516774832393</v>
+        <v>7.072190586030418</v>
       </c>
       <c r="H887" t="n">
-        <v>1.606307977763412</v>
+        <v>0.3158644007473974</v>
       </c>
       <c r="I887" t="n">
-        <v>37.57147572608734</v>
+        <v>7.388054986777815</v>
       </c>
       <c r="J887" t="inlineStr">
         <is>
@@ -37708,13 +37708,13 @@
         <v>0.101325</v>
       </c>
       <c r="G888" t="n">
-        <v>8.79257482556107</v>
+        <v>4.377207525409068</v>
       </c>
       <c r="H888" t="n">
-        <v>0.5626477678275281</v>
+        <v>0.2801029382575783</v>
       </c>
       <c r="I888" t="n">
-        <v>9.355222593388598</v>
+        <v>4.657310463666646</v>
       </c>
       <c r="J888" t="inlineStr">
         <is>
@@ -37750,13 +37750,13 @@
         <v>0.101325</v>
       </c>
       <c r="G889" t="n">
-        <v>10.77063239463337</v>
+        <v>4.817811576443451</v>
       </c>
       <c r="H889" t="n">
-        <v>0.6881633528740444</v>
+        <v>0.3078223493740888</v>
       </c>
       <c r="I889" t="n">
-        <v>11.45879574750741</v>
+        <v>5.12563392581754</v>
       </c>
       <c r="J889" t="inlineStr">
         <is>
@@ -37792,13 +37792,13 @@
         <v>0.101325</v>
       </c>
       <c r="G890" t="n">
-        <v>5.981947081901528</v>
+        <v>3.315793267498017</v>
       </c>
       <c r="H890" t="n">
-        <v>2.398529837157382</v>
+        <v>1.329505088736337</v>
       </c>
       <c r="I890" t="n">
-        <v>8.380476919058911</v>
+        <v>4.645298356234354</v>
       </c>
       <c r="J890" t="inlineStr">
         <is>
@@ -37834,13 +37834,13 @@
         <v>0.101325</v>
       </c>
       <c r="G891" t="n">
-        <v>4.576664275359582</v>
+        <v>2.710300583867944</v>
       </c>
       <c r="H891" t="n">
-        <v>3.091607554032279</v>
+        <v>1.830849993497915</v>
       </c>
       <c r="I891" t="n">
-        <v>7.668271829391861</v>
+        <v>4.54115057736586</v>
       </c>
       <c r="J891" t="inlineStr">
         <is>
@@ -37876,13 +37876,13 @@
         <v>0.101325</v>
       </c>
       <c r="G892" t="n">
-        <v>2.855749938006977</v>
+        <v>1.759713111799899</v>
       </c>
       <c r="H892" t="n">
-        <v>5.234300427012063</v>
+        <v>3.225375923124833</v>
       </c>
       <c r="I892" t="n">
-        <v>8.090050365019041</v>
+        <v>4.985089034924732</v>
       </c>
       <c r="J892" t="inlineStr">
         <is>
@@ -37918,13 +37918,13 @@
         <v>0.101325</v>
       </c>
       <c r="G893" t="n">
-        <v>0.5553523041680436</v>
+        <v>0.3532040654508757</v>
       </c>
       <c r="H893" t="n">
-        <v>8.738318901547682</v>
+        <v>5.557570821384326</v>
       </c>
       <c r="I893" t="n">
-        <v>9.293671205715725</v>
+        <v>5.910774886835202</v>
       </c>
       <c r="J893" t="inlineStr">
         <is>
